--- a/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260711.xlsx
+++ b/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260711.xlsx
@@ -2574,7 +2574,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-11 14:47</t>
+          <t>Generated: 2026-07-11 14:51</t>
         </is>
       </c>
     </row>
